--- a/output/Data and Chart Outputs/denmark_energinet_gasflow_daily.xlsx
+++ b/output/Data and Chart Outputs/denmark_energinet_gasflow_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Denmark gas supply by entry (Energinet) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -347,6 +348,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Denmark gas deliveries and exports (Energinet) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -915,7 +917,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GWh per gas day (the source is kWh). Positive = gas entering the Danish system, negative = leaving. DK_from_north_sea = North Sea entry (Danish fields plus Norwegian gas arriving through the offshore pipelines that supplies Baltic Pipe); DK_from_tyra = Tyra hub entry; DK_biogas = biomethane injected; DK_to_denmark = delivered to Danish consumers (negative); DK_storage = withdrawal (+) or injection (-) at Gas Storage Denmark; DK_germany = imports (+) / exports (-) at the German border; DK_to_sweden and DK_to_poland = exports. The columns net to about zero each day (linepack and allocation differences remain).</t>
+          <t>GWh per gas day (the source is kWh). Positive = gas entering the Danish system, negative = leaving. DK_from_north_sea = North Sea entry (zero until Baltic Pipe started in Oct 2022, then mainly Norwegian gas for Baltic Pipe); DK_from_tyra = Tyra hub entry (Danish fields, small until 2024); DK_biogas = biomethane injected; DK_to_denmark = delivered to Danish consumers (negative); DK_storage = withdrawal (+) or injection (-) at Gas Storage Denmark; DK_germany = imports (+) / exports (-) at the German border; DK_to_sweden and DK_to_poland = exports. The columns net to about zero each day (linepack and allocation differences remain).</t>
         </is>
       </c>
     </row>
@@ -937,7 +939,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 06:48 UTC; 2102 days, 2021-01-01 to 2026-10-03</t>
+          <t>2026-10-28 00:51 UTC; 2125 days, 2021-01-01 to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -966,12 +968,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>North Sea entry (Danish fields + Norwegian transit)</t>
+          <t>North Sea entry (mainly Norwegian gas for Baltic Pipe)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Tyra</t>
+          <t>Tyra (Danish fields)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -991,7 +993,7 @@
         <v>0.10416</v>
       </c>
       <c r="D2" t="n">
-        <v>0.472205</v>
+        <v>0.4722050000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1061,7 +1063,7 @@
         <v>0.03204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.472076</v>
+        <v>0.4720760000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1072,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0372</v>
+        <v>0.03720000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0.496042</v>
@@ -1086,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03715</v>
+        <v>0.03715000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.5279940000000001</v>
@@ -1103,7 +1105,7 @@
         <v>0.009509999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.504895</v>
+        <v>0.5048950000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1114,10 +1116,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04728</v>
+        <v>0.04727999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.549749</v>
+        <v>0.5497490000000002</v>
       </c>
     </row>
     <row r="12">
@@ -1128,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0456</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>0.553173</v>
@@ -1142,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03947999999999999</v>
+        <v>0.03948000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5778799999999999</v>
+        <v>0.5778799999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1159,7 +1161,7 @@
         <v>0.01052</v>
       </c>
       <c r="D14" t="n">
-        <v>0.563333</v>
+        <v>0.5633330000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1187,7 +1189,7 @@
         <v>0.05395</v>
       </c>
       <c r="D16" t="n">
-        <v>0.565313</v>
+        <v>0.5653130000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1198,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04175</v>
+        <v>0.04175000000000002</v>
       </c>
       <c r="D17" t="n">
-        <v>0.532794</v>
+        <v>0.5327940000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1215,7 +1217,7 @@
         <v>0.03576</v>
       </c>
       <c r="D18" t="n">
-        <v>0.544442</v>
+        <v>0.5444419999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1226,10 +1228,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.055968</v>
+        <v>0.05596799999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5375650000000001</v>
+        <v>0.537565</v>
       </c>
     </row>
     <row r="20">
@@ -1240,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0516</v>
+        <v>0.05159999999999999</v>
       </c>
       <c r="D20" t="n">
         <v>0.561101</v>
@@ -1254,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07842</v>
+        <v>0.07842000000000003</v>
       </c>
       <c r="D21" t="n">
         <v>0.5787340000000001</v>
@@ -1268,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07823999999999999</v>
+        <v>0.07823999999999998</v>
       </c>
       <c r="D22" t="n">
-        <v>0.613546</v>
+        <v>0.6135459999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1282,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09737</v>
+        <v>0.09737000000000001</v>
       </c>
       <c r="D23" t="n">
         <v>0.677276</v>
@@ -1296,10 +1298,10 @@
         <v>2.154036</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08292000000000001</v>
+        <v>0.08291999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.636254</v>
+        <v>0.6362540000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1310,7 +1312,7 @@
         <v>4.984332999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.086592</v>
+        <v>0.08659199999999996</v>
       </c>
       <c r="D25" t="n">
         <v>0.6465080000000001</v>
@@ -1321,13 +1323,13 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>6.459810999999999</v>
+        <v>6.459811000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.084744</v>
+        <v>0.08474400000000003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.679295</v>
+        <v>0.6792950000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1335,13 +1337,13 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>6.280329</v>
+        <v>6.280328999999999</v>
       </c>
       <c r="C27" t="n">
         <v>0.07415999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947749999999999</v>
+        <v>0.5947750000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1349,7 +1351,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>7.143849</v>
+        <v>7.143849000000001</v>
       </c>
       <c r="C28" t="n">
         <v>0.04478</v>
@@ -1363,10 +1365,10 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>6.222467</v>
+        <v>6.222467000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.072806</v>
+        <v>0.07280600000000001</v>
       </c>
       <c r="D29" t="n">
         <v>0.657393</v>
@@ -1380,7 +1382,7 @@
         <v>5.206942</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0696</v>
+        <v>0.06960000000000001</v>
       </c>
       <c r="D30" t="n">
         <v>0.686952</v>
@@ -1397,7 +1399,7 @@
         <v>0.05648</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6564800000000001</v>
+        <v>0.65648</v>
       </c>
     </row>
     <row r="32">
@@ -1405,7 +1407,7 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>7.537782</v>
+        <v>7.537781999999998</v>
       </c>
       <c r="C32" t="n">
         <v>0.01626</v>
@@ -1422,10 +1424,10 @@
         <v>7.325395</v>
       </c>
       <c r="C33" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.08840000000000002</v>
       </c>
       <c r="D33" t="n">
-        <v>0.679042</v>
+        <v>0.6790420000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1436,10 +1438,10 @@
         <v>6.542396</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08353000000000001</v>
+        <v>0.08352999999999998</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6652830000000001</v>
+        <v>0.6652829999999998</v>
       </c>
     </row>
     <row r="35">
@@ -1447,10 +1449,10 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>7.922661</v>
+        <v>7.922661000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.08106000000000001</v>
+        <v>0.08106000000000003</v>
       </c>
       <c r="D35" t="n">
         <v>0.7005739999999999</v>
@@ -1481,7 +1483,7 @@
         <v>0.07986</v>
       </c>
       <c r="D37" t="n">
-        <v>0.664649</v>
+        <v>0.6646489999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1492,10 +1494,10 @@
         <v>8.701231</v>
       </c>
       <c r="C38" t="n">
-        <v>0.06711</v>
+        <v>0.06711000000000002</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6899</v>
+        <v>0.6898999999999998</v>
       </c>
     </row>
     <row r="39">
@@ -1506,10 +1508,10 @@
         <v>7.043577</v>
       </c>
       <c r="C39" t="n">
-        <v>0.073305</v>
+        <v>0.07330500000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6412340000000001</v>
+        <v>0.641234</v>
       </c>
     </row>
     <row r="40">
@@ -1523,7 +1525,7 @@
         <v>0.070233</v>
       </c>
       <c r="D40" t="n">
-        <v>0.692534</v>
+        <v>0.6925340000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1531,13 +1533,13 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>7.596938</v>
+        <v>7.596937999999997</v>
       </c>
       <c r="C41" t="n">
         <v>0.522778</v>
       </c>
       <c r="D41" t="n">
-        <v>0.654726</v>
+        <v>0.6547260000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1551,7 +1553,7 @@
         <v>0.199171</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6708999999999999</v>
+        <v>0.6708999999999998</v>
       </c>
     </row>
     <row r="43">
@@ -1562,10 +1564,10 @@
         <v>8.823508</v>
       </c>
       <c r="C43" t="n">
-        <v>0.327334</v>
+        <v>0.3273340000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6483239999999999</v>
+        <v>0.6483240000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1573,7 +1575,7 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>9.458457000000001</v>
+        <v>9.458456999999999</v>
       </c>
       <c r="C44" t="n">
         <v>0.198198</v>
@@ -1593,7 +1595,7 @@
         <v>0.471822</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6824199999999999</v>
+        <v>0.6824199999999998</v>
       </c>
     </row>
     <row r="46">
@@ -1607,7 +1609,7 @@
         <v>0.469018</v>
       </c>
       <c r="D46" t="n">
-        <v>0.678015</v>
+        <v>0.6780150000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1618,7 +1620,7 @@
         <v>8.957118000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>0.664376</v>
+        <v>0.6643759999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0.70621</v>
@@ -1632,7 +1634,7 @@
         <v>8.353187</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6668229999999999</v>
+        <v>0.6668230000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0.6968840000000001</v>
@@ -1688,7 +1690,7 @@
         <v>7.471277</v>
       </c>
       <c r="C52" t="n">
-        <v>0.265104</v>
+        <v>0.2651040000000001</v>
       </c>
       <c r="D52" t="n">
         <v>0.744068</v>
@@ -1699,7 +1701,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>6.378719</v>
+        <v>6.378719000000001</v>
       </c>
       <c r="C53" t="n">
         <v>0.7302909999999999</v>
@@ -1719,7 +1721,7 @@
         <v>1.29265</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7255470000000001</v>
+        <v>0.7255469999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1727,13 +1729,13 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>7.619714</v>
+        <v>7.619714000000001</v>
       </c>
       <c r="C55" t="n">
         <v>1.209899</v>
       </c>
       <c r="D55" t="n">
-        <v>0.675714</v>
+        <v>0.6757139999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1761,7 +1763,7 @@
         <v>1.335465</v>
       </c>
       <c r="D57" t="n">
-        <v>0.670311</v>
+        <v>0.6703110000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1789,7 +1791,7 @@
         <v>1.276048</v>
       </c>
       <c r="D59" t="n">
-        <v>0.691119</v>
+        <v>0.6911189999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1817,7 +1819,7 @@
         <v>2.056385</v>
       </c>
       <c r="D61" t="n">
-        <v>0.684659</v>
+        <v>0.6846590000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1825,7 +1827,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>9.805628</v>
+        <v>9.805627999999999</v>
       </c>
       <c r="C62" t="n">
         <v>2.192898</v>
@@ -1839,13 +1841,13 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>8.941317</v>
+        <v>8.941317000000002</v>
       </c>
       <c r="C63" t="n">
         <v>2.056031</v>
       </c>
       <c r="D63" t="n">
-        <v>0.634038</v>
+        <v>0.6340380000000001</v>
       </c>
     </row>
     <row r="64">
@@ -1867,13 +1869,13 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>6.111446</v>
+        <v>6.111445999999999</v>
       </c>
       <c r="C65" t="n">
         <v>2.316575</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7226359999999999</v>
+        <v>0.7226360000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1881,13 +1883,13 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>6.739056</v>
+        <v>6.739056000000001</v>
       </c>
       <c r="C66" t="n">
         <v>2.076102</v>
       </c>
       <c r="D66" t="n">
-        <v>0.757698</v>
+        <v>0.7576980000000002</v>
       </c>
     </row>
     <row r="67">
@@ -1895,7 +1897,7 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>6.535939</v>
+        <v>6.535938999999999</v>
       </c>
       <c r="C67" t="n">
         <v>1.510956</v>
@@ -1912,7 +1914,7 @@
         <v>6.023819</v>
       </c>
       <c r="C68" t="n">
-        <v>2.523295</v>
+        <v>2.523295000000001</v>
       </c>
       <c r="D68" t="n">
         <v>0.7862210000000001</v>
@@ -1937,13 +1939,13 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>4.048989</v>
+        <v>4.048988999999999</v>
       </c>
       <c r="C70" t="n">
         <v>2.368985</v>
       </c>
       <c r="D70" t="n">
-        <v>0.770609</v>
+        <v>0.7706090000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2904,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2103"/>
+  <dimension ref="A1:I2126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61998,10 +62000,677 @@
         <v>-2.699</v>
       </c>
       <c r="H2103" t="n">
-        <v>-10.368</v>
+        <v>-10.367</v>
       </c>
       <c r="I2103" t="n">
         <v>-230.575</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>163.949</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>91.617</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>-36.831</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>-10.689</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>-230.575</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>162.938</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>87.67100000000001</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>26.054</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>-44.598</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>-12.647</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>-226.495</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>175.508</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>85.852</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>25.499</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>-47.83</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>-13.456</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>89.161</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>26.049</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>-50.846</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>-5.674</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>-13.555</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>184.411</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>88.761</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>-44.969</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>-4.561</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>-13.552</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>194.515</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>87.259</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>27.273</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>-41.623</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>-25.837</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>-1.853</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>-12.394</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>174.261</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>88.398</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>27.352</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>-38.152</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>-5.519</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>-9.353999999999999</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>167.944</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>86.96299999999999</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>26.944</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>-45.23</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>-6.057</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>-3.603</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>-10.71</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>166.41</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>88.71299999999999</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>26.111</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>-56.892</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>8.736000000000001</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>-14.39</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>-226.403</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>197.112</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>87.46599999999999</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>26.445</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>-51.622</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>-13.755</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>197.918</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>83.617</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>27.098</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>-50.048</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>-18.383</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>-0.134</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>-13.555</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>-230.579</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>216.985</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>85.161</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>27.438</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>-49.254</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>-28.836</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>-12.305</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>-230.583</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>207.055</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>90.92700000000001</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>27.407</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>-44.644</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>-38.363</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>-10.958</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>-230.583</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>199.333</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>87.04600000000001</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>27.527</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>-43.108</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>-30.015</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>-10.886</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>199.333</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>63.311</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>27.052</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>-47.075</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>-3.408</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>-0.293</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>-13.491</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>184.054</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>90.252</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>26.221</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>-59.822</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>-5.333</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>-16.643</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>-226.826</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>226.68</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>93.824</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>25.703</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>-60.13</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>-15.408</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>-15.55</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>251.924</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>81.601</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>25.891</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>-57.454</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>-53.791</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>-14.834</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>202.86</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>87.22799999999999</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>26.236</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>-53.932</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>-26.48</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>-15.964</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>200.989</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>26.791</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>-47.765</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>-17.126</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>-15.531</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>-230.586</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>200.076</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>27.856</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>-44.33</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>-27.71</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>-0.368</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>-13.685</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>-234.248</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>182.759</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>89.125</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>24.918</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>-44.709</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>-0.223</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>-13.077</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>-230.583</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>181.02</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>88.857</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>25.471</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>-52.783</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>-8.144</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>3.482</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>-13.827</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>-225.783</v>
       </c>
     </row>
   </sheetData>
